--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,6 +120,14 @@
   </si>
   <si>
     <t>RSI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业LOF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -697,7 +705,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1027,6 +1035,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1036,7 +1047,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1366,6 +1377,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>220000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>222000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1408,7 +1422,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1738,6 +1752,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1747,7 +1764,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2077,6 +2094,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>542783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>613430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2119,7 +2139,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2449,6 +2469,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2458,7 +2481,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2788,6 +2811,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>322783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>391430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2809,11 +2835,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="459649408"/>
-        <c:axId val="459650944"/>
+        <c:axId val="503205248"/>
+        <c:axId val="504555008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="459649408"/>
+        <c:axId val="503205248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2853,14 +2879,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459650944"/>
+        <c:crossAx val="504555008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459650944"/>
+        <c:axId val="504555008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2909,7 +2935,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459649408"/>
+        <c:crossAx val="503205248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3039,7 +3065,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3369,6 +3395,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3378,7 +3407,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3708,6 +3737,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>220000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>222000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3741,7 +3773,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4071,6 +4103,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4080,7 +4115,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4410,6 +4445,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>542783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>613430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4443,7 +4481,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4773,6 +4811,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4782,7 +4823,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5112,6 +5153,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>322783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>391430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5133,11 +5177,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501033600"/>
-        <c:axId val="501068544"/>
+        <c:axId val="504617216"/>
+        <c:axId val="504632064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501033600"/>
+        <c:axId val="504617216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5147,14 +5191,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="501068544"/>
+        <c:crossAx val="504632064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501068544"/>
+        <c:axId val="504632064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5165,7 +5209,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="501033600"/>
+        <c:crossAx val="504617216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5287,7 +5331,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5617,6 +5661,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5626,7 +5673,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5956,6 +6003,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5998,7 +6048,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6328,6 +6378,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6337,7 +6390,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6667,6 +6720,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>567445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>641210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6709,7 +6765,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7039,6 +7095,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7048,7 +7107,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7378,6 +7437,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>340445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>412210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7399,11 +7461,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501081600"/>
-        <c:axId val="501083520"/>
+        <c:axId val="465556608"/>
+        <c:axId val="465558144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501081600"/>
+        <c:axId val="465556608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7443,14 +7505,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501083520"/>
+        <c:crossAx val="465558144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501083520"/>
+        <c:axId val="465558144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7499,7 +7561,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501081600"/>
+        <c:crossAx val="465556608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7629,7 +7691,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7959,6 +8021,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7968,7 +8033,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8298,6 +8363,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8331,7 +8399,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8661,6 +8729,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8670,7 +8741,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9000,6 +9071,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>567445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>641210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9033,7 +9107,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9363,6 +9437,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9372,7 +9449,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9702,6 +9779,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>340445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>412210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9723,11 +9803,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="614936960"/>
-        <c:axId val="614938880"/>
+        <c:axId val="466896384"/>
+        <c:axId val="466897920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="614936960"/>
+        <c:axId val="466896384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9737,14 +9817,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="614938880"/>
+        <c:crossAx val="466897920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614938880"/>
+        <c:axId val="466897920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9755,7 +9835,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="614936960"/>
+        <c:crossAx val="466896384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9877,7 +9957,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10207,6 +10287,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10216,7 +10299,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10546,6 +10629,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10588,7 +10674,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10918,6 +11004,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10927,7 +11016,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11257,6 +11346,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>565611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>639144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11299,7 +11391,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11629,6 +11721,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11638,7 +11733,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11968,6 +12063,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>338611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>410144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11989,11 +12087,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="497587712"/>
-        <c:axId val="497589248"/>
+        <c:axId val="466938112"/>
+        <c:axId val="467075072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="497587712"/>
+        <c:axId val="466938112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12033,14 +12131,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="497589248"/>
+        <c:crossAx val="467075072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="497589248"/>
+        <c:axId val="467075072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12089,7 +12187,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="497587712"/>
+        <c:crossAx val="466938112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12219,7 +12317,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12549,6 +12647,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12558,7 +12659,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12888,6 +12989,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12921,7 +13025,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13251,6 +13355,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13260,7 +13367,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13590,6 +13697,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>565611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>639144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13623,7 +13733,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13953,6 +14063,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13962,7 +14075,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14292,6 +14405,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>338611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>410144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14313,11 +14429,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="497624960"/>
-        <c:axId val="497626496"/>
+        <c:axId val="467098240"/>
+        <c:axId val="467108224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="497624960"/>
+        <c:axId val="467098240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14327,14 +14443,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="497626496"/>
+        <c:crossAx val="467108224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="497626496"/>
+        <c:axId val="467108224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14345,7 +14461,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="497624960"/>
+        <c:crossAx val="467098240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14387,7 +14503,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14425,7 +14541,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14466,7 +14582,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14504,7 +14620,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14547,7 +14663,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14585,7 +14701,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14863,7 +14979,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14872,7 +14988,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB112"/>
+  <dimension ref="A1:AB113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18826,6 +18942,35 @@
         <v>322783.95352470258</v>
       </c>
     </row>
+    <row r="113" spans="1:9" ht="12.75">
+      <c r="A113" s="13">
+        <v>46203</v>
+      </c>
+      <c r="B113" s="18">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C113" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D113" s="15">
+        <v>580.21467493663954</v>
+      </c>
+      <c r="E113" s="15">
+        <v>177960.59496071746</v>
+      </c>
+      <c r="F113" s="15">
+        <v>613430.1755816536</v>
+      </c>
+      <c r="G113" s="15">
+        <v>222000</v>
+      </c>
+      <c r="H113" s="15">
+        <v>613430.1755816536</v>
+      </c>
+      <c r="I113" s="15">
+        <v>391430.1755816536</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18837,7 +18982,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24508,6 +24653,50 @@
         <v>74.805935689687729</v>
       </c>
     </row>
+    <row r="113" spans="1:14" ht="12.75">
+      <c r="A113" s="13">
+        <v>46203</v>
+      </c>
+      <c r="B113" s="18">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C113" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D113" s="15">
+        <v>580.21467493663954</v>
+      </c>
+      <c r="E113" s="15">
+        <v>186019.93581855964</v>
+      </c>
+      <c r="F113" s="15">
+        <v>641210.7237338433</v>
+      </c>
+      <c r="G113" s="15">
+        <v>229000</v>
+      </c>
+      <c r="H113" s="15">
+        <v>641210.7237338433</v>
+      </c>
+      <c r="I113" s="15">
+        <v>412210.7237338433</v>
+      </c>
+      <c r="J113" s="21">
+        <v>0.38700008392333984</v>
+      </c>
+      <c r="K113" s="21">
+        <v>0.22298399794060811</v>
+      </c>
+      <c r="L113" s="21">
+        <v>0.38700008392333984</v>
+      </c>
+      <c r="M113" s="23">
+        <v>0.27636018590033579</v>
+      </c>
+      <c r="N113" s="21">
+        <v>80.686006638099158</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24519,7 +24708,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24548,10 +24737,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>2</v>
@@ -24575,28 +24764,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -24606,7 +24795,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -31067,6 +31256,59 @@
         <v>90.125507288989468</v>
       </c>
     </row>
+    <row r="113" spans="1:17" ht="12.75">
+      <c r="A113" s="13">
+        <v>46203</v>
+      </c>
+      <c r="B113" s="18">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C113" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D113" s="15">
+        <v>580.21467493663954</v>
+      </c>
+      <c r="E113" s="15">
+        <v>185420.63592600022</v>
+      </c>
+      <c r="F113" s="15">
+        <v>639144.93698818795</v>
+      </c>
+      <c r="G113" s="15">
+        <v>229000</v>
+      </c>
+      <c r="H113" s="15">
+        <v>639144.93698818795</v>
+      </c>
+      <c r="I113" s="15">
+        <v>410144.93698818795</v>
+      </c>
+      <c r="J113" s="15">
+        <v>3.4479999542236328</v>
+      </c>
+      <c r="K113" s="15">
+        <v>2.8849999904632568</v>
+      </c>
+      <c r="L113" s="19">
+        <v>3.4479999542236328</v>
+      </c>
+      <c r="M113" s="19">
+        <v>2.1180000305175781</v>
+      </c>
+      <c r="N113" s="21">
+        <v>99.924817475329945</v>
+      </c>
+      <c r="O113" s="21">
+        <v>87.572495182046978</v>
+      </c>
+      <c r="P113" s="21">
+        <v>80.545329999757996</v>
+      </c>
+      <c r="Q113" s="21">
+        <v>101.62682554662496</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,11 +123,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>人工智能产业LOF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -161,10 +169,6 @@
   <si>
     <t>J</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -705,7 +709,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1038,6 +1042,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1047,7 +1054,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1380,6 +1387,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>222000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>224000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1422,7 +1432,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1755,6 +1765,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1764,7 +1777,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2097,6 +2110,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>613430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>500823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2139,7 +2155,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2472,6 +2488,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2481,7 +2500,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2814,6 +2833,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>391430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>276823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2835,11 +2857,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="503205248"/>
-        <c:axId val="504555008"/>
+        <c:axId val="591437184"/>
+        <c:axId val="591501184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="503205248"/>
+        <c:axId val="591437184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2879,14 +2901,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="504555008"/>
+        <c:crossAx val="591501184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="504555008"/>
+        <c:axId val="591501184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2935,7 +2957,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="503205248"/>
+        <c:crossAx val="591437184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3065,7 +3087,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3398,6 +3420,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3407,7 +3432,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3740,6 +3765,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>222000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>224000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3773,7 +3801,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4106,6 +4134,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4115,7 +4146,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4448,6 +4479,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>613430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>500823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4481,7 +4515,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4814,6 +4848,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4823,7 +4860,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5156,6 +5193,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>391430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>276823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5177,11 +5217,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="504617216"/>
-        <c:axId val="504632064"/>
+        <c:axId val="591570816"/>
+        <c:axId val="591581184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="504617216"/>
+        <c:axId val="591570816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5191,14 +5231,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="504632064"/>
+        <c:crossAx val="591581184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="504632064"/>
+        <c:axId val="591581184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5209,7 +5249,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="504617216"/>
+        <c:crossAx val="591570816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5331,7 +5371,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5664,6 +5704,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5673,7 +5716,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6006,6 +6049,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6048,7 +6094,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6381,6 +6427,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6390,7 +6439,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6723,6 +6772,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>641210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>523413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6765,7 +6817,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7098,6 +7150,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7107,7 +7162,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7440,6 +7495,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>412210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>292413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7461,11 +7519,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="465556608"/>
-        <c:axId val="465558144"/>
+        <c:axId val="522845568"/>
+        <c:axId val="522876032"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="465556608"/>
+        <c:axId val="522845568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7505,14 +7563,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465558144"/>
+        <c:crossAx val="522876032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465558144"/>
+        <c:axId val="522876032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7561,7 +7619,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465556608"/>
+        <c:crossAx val="522845568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7691,7 +7749,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8024,6 +8082,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8033,7 +8094,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8366,6 +8427,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8399,7 +8463,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8732,6 +8796,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8741,7 +8808,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9074,6 +9141,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>641210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>523413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9107,7 +9177,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9440,6 +9510,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9449,7 +9522,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9782,6 +9855,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>412210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>292413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9803,11 +9879,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="466896384"/>
-        <c:axId val="466897920"/>
+        <c:axId val="522899456"/>
+        <c:axId val="522900992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="466896384"/>
+        <c:axId val="522899456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9817,14 +9893,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="466897920"/>
+        <c:crossAx val="522900992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466897920"/>
+        <c:axId val="522900992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9835,7 +9911,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="466896384"/>
+        <c:crossAx val="522899456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9957,7 +10033,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10290,6 +10366,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10299,7 +10378,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10632,6 +10711,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10674,7 +10756,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11007,6 +11089,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11016,7 +11101,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11349,6 +11434,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>639144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>521734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11391,7 +11479,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11724,6 +11812,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11733,7 +11824,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12066,6 +12157,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>410144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>290734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12087,11 +12181,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="466938112"/>
-        <c:axId val="467075072"/>
+        <c:axId val="523113216"/>
+        <c:axId val="523114752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="466938112"/>
+        <c:axId val="523113216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12131,14 +12225,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467075072"/>
+        <c:crossAx val="523114752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467075072"/>
+        <c:axId val="523114752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12187,7 +12281,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466938112"/>
+        <c:crossAx val="523113216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12317,7 +12411,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12650,6 +12744,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12659,7 +12756,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12992,6 +13089,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13025,7 +13125,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13358,6 +13458,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13367,7 +13470,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13700,6 +13803,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>639144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>521734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13733,7 +13839,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14066,6 +14172,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14075,7 +14184,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14408,6 +14517,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>410144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>290734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14429,11 +14541,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467098240"/>
-        <c:axId val="467108224"/>
+        <c:axId val="522814592"/>
+        <c:axId val="522816128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467098240"/>
+        <c:axId val="522814592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14443,14 +14555,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="467108224"/>
+        <c:crossAx val="522816128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467108224"/>
+        <c:axId val="522816128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14461,7 +14573,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="467098240"/>
+        <c:crossAx val="522814592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14503,7 +14615,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14541,7 +14653,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14582,7 +14694,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14620,7 +14732,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14663,7 +14775,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14701,7 +14813,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14979,7 +15091,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14988,7 +15100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB113"/>
+  <dimension ref="A1:AB114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18971,6 +19083,35 @@
         <v>391430.1755816536</v>
       </c>
     </row>
+    <row r="114" spans="1:9" ht="12.75">
+      <c r="A114" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B114" s="18">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C114" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D114" s="15">
+        <v>713.52123405389671</v>
+      </c>
+      <c r="E114" s="15">
+        <v>178674.11619477134</v>
+      </c>
+      <c r="F114" s="15">
+        <v>500823.54292283044</v>
+      </c>
+      <c r="G114" s="15">
+        <v>224000</v>
+      </c>
+      <c r="H114" s="15">
+        <v>500823.54292283044</v>
+      </c>
+      <c r="I114" s="15">
+        <v>276823.54292283044</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18982,7 +19123,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -19060,7 +19201,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -24695,6 +24836,50 @@
       </c>
       <c r="N113" s="21">
         <v>80.686006638099158</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="12.75">
+      <c r="A114" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B114" s="18">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C114" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D114" s="15">
+        <v>713.52123405389671</v>
+      </c>
+      <c r="E114" s="15">
+        <v>186733.45705261352</v>
+      </c>
+      <c r="F114" s="15">
+        <v>523413.87513215444</v>
+      </c>
+      <c r="G114" s="15">
+        <v>231000</v>
+      </c>
+      <c r="H114" s="15">
+        <v>523413.87513215444</v>
+      </c>
+      <c r="I114" s="15">
+        <v>292413.87513215444</v>
+      </c>
+      <c r="J114" s="21">
+        <v>0</v>
+      </c>
+      <c r="K114" s="21">
+        <v>0.1858199982838401</v>
+      </c>
+      <c r="L114" s="21">
+        <v>0.64400005340576172</v>
+      </c>
+      <c r="M114" s="23">
+        <v>0.33763349715124008</v>
+      </c>
+      <c r="N114" s="21">
+        <v>55.036007935137903</v>
       </c>
     </row>
   </sheetData>
@@ -24708,7 +24893,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24737,13 +24922,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -24764,28 +24949,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -24795,7 +24980,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -31309,6 +31494,59 @@
         <v>101.62682554662496</v>
       </c>
     </row>
+    <row r="114" spans="1:17" ht="12.75">
+      <c r="A114" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B114" s="18">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C114" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D114" s="15">
+        <v>713.52123405389671</v>
+      </c>
+      <c r="E114" s="15">
+        <v>186134.15716005411</v>
+      </c>
+      <c r="F114" s="15">
+        <v>521734.03754931345</v>
+      </c>
+      <c r="G114" s="15">
+        <v>231000</v>
+      </c>
+      <c r="H114" s="15">
+        <v>521734.03754931345</v>
+      </c>
+      <c r="I114" s="15">
+        <v>290734.03754931345</v>
+      </c>
+      <c r="J114" s="15">
+        <v>3.5380001068115234</v>
+      </c>
+      <c r="K114" s="15">
+        <v>2.687000036239624</v>
+      </c>
+      <c r="L114" s="19">
+        <v>3.5380001068115234</v>
+      </c>
+      <c r="M114" s="19">
+        <v>2.1180000305175781</v>
+      </c>
+      <c r="N114" s="21">
+        <v>48.239429998294135</v>
+      </c>
+      <c r="O114" s="21">
+        <v>74.461473454129361</v>
+      </c>
+      <c r="P114" s="21">
+        <v>78.51737781788178</v>
+      </c>
+      <c r="Q114" s="21">
+        <v>66.349664726624525</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,6 +103,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>MAX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -125,18 +129,6 @@
   <si>
     <t>单位：元</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -709,7 +701,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1045,6 +1037,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1054,7 +1049,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1390,6 +1385,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>224000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>226000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1432,7 +1430,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1768,6 +1766,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1777,7 +1778,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2113,6 +2114,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>500823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>503538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2155,7 +2159,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2491,6 +2495,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2500,7 +2507,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2836,6 +2843,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>276823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>277538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2857,11 +2867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="591437184"/>
-        <c:axId val="591501184"/>
+        <c:axId val="458058368"/>
+        <c:axId val="458068736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="591437184"/>
+        <c:axId val="458058368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2901,14 +2911,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591501184"/>
+        <c:crossAx val="458068736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="591501184"/>
+        <c:axId val="458068736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2957,7 +2967,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591437184"/>
+        <c:crossAx val="458058368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3087,7 +3097,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3423,6 +3433,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3432,7 +3445,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3768,6 +3781,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>224000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>226000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3801,7 +3817,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4137,6 +4153,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4146,7 +4165,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4482,6 +4501,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>500823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>503538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4515,7 +4537,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4851,6 +4873,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4860,7 +4885,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5196,6 +5221,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>276823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>277538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5217,11 +5245,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="591570816"/>
-        <c:axId val="591581184"/>
+        <c:axId val="514372736"/>
+        <c:axId val="514374272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="591570816"/>
+        <c:axId val="514372736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5231,14 +5259,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="591581184"/>
+        <c:crossAx val="514374272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="591581184"/>
+        <c:axId val="514374272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5249,7 +5277,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="591570816"/>
+        <c:crossAx val="514372736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5371,7 +5399,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5707,6 +5735,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5716,7 +5747,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6052,6 +6083,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6094,7 +6128,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6430,6 +6464,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6439,7 +6476,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6775,6 +6812,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>523413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>526160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6817,7 +6857,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7153,6 +7193,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7162,7 +7205,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7498,6 +7541,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>292413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>293160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7519,11 +7565,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522845568"/>
-        <c:axId val="522876032"/>
+        <c:axId val="520064384"/>
+        <c:axId val="520074368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522845568"/>
+        <c:axId val="520064384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7563,14 +7609,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522876032"/>
+        <c:crossAx val="520074368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522876032"/>
+        <c:axId val="520074368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7619,7 +7665,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522845568"/>
+        <c:crossAx val="520064384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7749,7 +7795,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8085,6 +8131,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8094,7 +8143,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8430,6 +8479,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8463,7 +8515,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8799,6 +8851,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8808,7 +8863,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9144,6 +9199,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>523413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>526160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9177,7 +9235,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9513,6 +9571,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9522,7 +9583,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9858,6 +9919,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>292413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>293160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9879,11 +9943,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522899456"/>
-        <c:axId val="522900992"/>
+        <c:axId val="520298496"/>
+        <c:axId val="520300032"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522899456"/>
+        <c:axId val="520298496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9893,14 +9957,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522900992"/>
+        <c:crossAx val="520300032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522900992"/>
+        <c:axId val="520300032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9911,7 +9975,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522899456"/>
+        <c:crossAx val="520298496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10033,7 +10097,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10369,6 +10433,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10378,7 +10445,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10714,6 +10781,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10756,7 +10826,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11092,6 +11162,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11101,7 +11174,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11437,6 +11510,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>521734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>524478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11479,7 +11555,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11815,6 +11891,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11824,7 +11903,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12160,6 +12239,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>290734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>291478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12181,11 +12263,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523113216"/>
-        <c:axId val="523114752"/>
+        <c:axId val="523854592"/>
+        <c:axId val="523856128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523113216"/>
+        <c:axId val="523854592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12225,14 +12307,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523114752"/>
+        <c:crossAx val="523856128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523114752"/>
+        <c:axId val="523856128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12281,7 +12363,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523113216"/>
+        <c:crossAx val="523854592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12411,7 +12493,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12747,6 +12829,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12756,7 +12841,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13092,6 +13177,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13125,7 +13213,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13461,6 +13549,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13470,7 +13561,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13806,6 +13897,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>521734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>524478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13839,7 +13933,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14175,6 +14269,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14184,7 +14281,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14520,6 +14617,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>290734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>291478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14541,11 +14641,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522814592"/>
-        <c:axId val="522816128"/>
+        <c:axId val="523883648"/>
+        <c:axId val="523885184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522814592"/>
+        <c:axId val="523883648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14555,14 +14655,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522816128"/>
+        <c:crossAx val="523885184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522816128"/>
+        <c:axId val="523885184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14573,7 +14673,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522814592"/>
+        <c:crossAx val="523883648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14615,7 +14715,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14653,7 +14753,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14694,7 +14794,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14732,7 +14832,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14775,7 +14875,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14813,7 +14913,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15091,7 +15191,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15100,7 +15200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB114"/>
+  <dimension ref="A1:AB115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -19112,6 +19212,35 @@
         <v>276823.54292283044</v>
       </c>
     </row>
+    <row r="115" spans="1:9" ht="12.75">
+      <c r="A115" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B115" s="18">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C115" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D115" s="15">
+        <v>712.50447300276869</v>
+      </c>
+      <c r="E115" s="15">
+        <v>179386.62066777411</v>
+      </c>
+      <c r="F115" s="15">
+        <v>503538.23018617608</v>
+      </c>
+      <c r="G115" s="15">
+        <v>226000</v>
+      </c>
+      <c r="H115" s="15">
+        <v>503538.23018617608</v>
+      </c>
+      <c r="I115" s="15">
+        <v>277538.23018617608</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19123,7 +19252,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -19152,7 +19281,7 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
@@ -19179,19 +19308,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -19201,7 +19330,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -24880,6 +25009,50 @@
       </c>
       <c r="N114" s="21">
         <v>55.036007935137903</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="12.75">
+      <c r="A115" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B115" s="18">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C115" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D115" s="15">
+        <v>712.50447300276869</v>
+      </c>
+      <c r="E115" s="15">
+        <v>187445.96152561629</v>
+      </c>
+      <c r="F115" s="15">
+        <v>526160.79934388818</v>
+      </c>
+      <c r="G115" s="15">
+        <v>233000</v>
+      </c>
+      <c r="H115" s="15">
+        <v>526160.79934388818</v>
+      </c>
+      <c r="I115" s="15">
+        <v>293160.79934388818</v>
+      </c>
+      <c r="J115" s="21">
+        <v>3.9999485015869141E-3</v>
+      </c>
+      <c r="K115" s="21">
+        <v>0.15551665665346456</v>
+      </c>
+      <c r="L115" s="21">
+        <v>3.9999485015869141E-3</v>
+      </c>
+      <c r="M115" s="23">
+        <v>0.28202790570963121</v>
+      </c>
+      <c r="N115" s="21">
+        <v>55.142293902497926</v>
       </c>
     </row>
   </sheetData>
@@ -24893,7 +25066,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24922,13 +25095,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -24949,28 +25122,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="P1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>31</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -24980,7 +25153,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -31547,6 +31720,59 @@
         <v>66.349664726624525</v>
       </c>
     </row>
+    <row r="115" spans="1:17" ht="12.75">
+      <c r="A115" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B115" s="18">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C115" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D115" s="15">
+        <v>712.50447300276869</v>
+      </c>
+      <c r="E115" s="15">
+        <v>186846.66163305688</v>
+      </c>
+      <c r="F115" s="15">
+        <v>524478.56459233991</v>
+      </c>
+      <c r="G115" s="15">
+        <v>233000</v>
+      </c>
+      <c r="H115" s="15">
+        <v>524478.56459233991</v>
+      </c>
+      <c r="I115" s="15">
+        <v>291478.56459233991</v>
+      </c>
+      <c r="J115" s="15">
+        <v>2.9820001125335693</v>
+      </c>
+      <c r="K115" s="15">
+        <v>2.6749999523162842</v>
+      </c>
+      <c r="L115" s="19">
+        <v>3.5380001068115234</v>
+      </c>
+      <c r="M115" s="19">
+        <v>2.2260000705718994</v>
+      </c>
+      <c r="N115" s="21">
+        <v>44.283524022760979</v>
+      </c>
+      <c r="O115" s="21">
+        <v>64.40215697700657</v>
+      </c>
+      <c r="P115" s="21">
+        <v>73.812304204256705</v>
+      </c>
+      <c r="Q115" s="21">
+        <v>45.581862522506299</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
